--- a/05_statistics/pathway_conflict_report.xlsx
+++ b/05_statistics/pathway_conflict_report.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D24"/>
+  <dimension ref="A1:D7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -453,7 +453,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>ETOH_005</t>
+          <t>ETOH_009</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -463,63 +463,63 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>P1;P5</t>
+          <t>P2;P5</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>{'final_mentioned_pathways': 'P1;P5', 'final_main_pathways': 'P1;P5', 'final_rejected_pathways': 'P5', 'ethanol_specific_level': 'yes', 'main_evidence_basis': 'DFT;DFT;operando/spectroscopy;operando/spectroscopy;operando/spectroscopy;product inference;unknown', 'ai_paper_reason': 'Sentence-level AI review found main-pathway evidence for P1;P5.', 'ai_paper_confidence': 'low', 'final_include': 'yes'}</t>
+          <t>{'final_mentioned_pathways': 'P2;P5', 'final_main_pathways': 'P2;P5', 'final_rejected_pathways': nan, 'ethanol_specific_level': 'yes', 'main_evidence_basis': 'mixed', 'ai_paper_reason': 'The paper proposes a tandem catalyst with dual active sites (Sn and O) that enable C-C coupling between *CHO and *CO(OH) (P2) and between formate/HCOOH and *CO(OH) (P5) to form ethanol. Evidence includes DFT calculations, isotope labeling, and product distribution experiments.', 'ai_paper_confidence': 'high', 'final_include': 'yes'}</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>ETOH_005</t>
+          <t>ETOH_016</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>same_pathway_main_and_reject</t>
+          <t>multiple_main_pathways</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>P5</t>
+          <t>P1;P3;P6</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>{'final_mentioned_pathways': 'P1;P5', 'final_main_pathways': 'P1;P5', 'final_rejected_pathways': 'P5', 'ethanol_specific_level': 'yes', 'main_evidence_basis': 'DFT;DFT;operando/spectroscopy;operando/spectroscopy;operando/spectroscopy;product inference;unknown', 'ai_paper_reason': 'Sentence-level AI review found main-pathway evidence for P1;P5.', 'ai_paper_confidence': 'low', 'final_include': 'yes'}</t>
+          <t>{'final_mentioned_pathways': 'P1;P3;P6', 'final_main_pathways': 'P1;P3;P6', 'final_rejected_pathways': 'P6', 'ethanol_specific_level': 'partial', 'main_evidence_basis': 'mixed', 'ai_paper_reason': '该文献主要基于原位拉曼光谱（SERS）和DFT计算，识别了CO2还原制乙烯和乙醇的关键中间体。统计句显示P1（OCCO路径）、P3（*CHCO→*OCHCH2路径）和P6（*OCHCH路径）是主要提及路径，其中P3和P6明确指向乙醇，P1主要指向乙烯。同时，DFT计算排除了P6（CO-CH耦合）在缺陷位上的主导作用，但实验SERS证实了*OCHCH中间体。因此，文献级路径存在部分冲突，但整体上乙醇路径证据明确。', 'ai_paper_confidence': 'medium', 'final_include': 'yes'}</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>ETOH_005</t>
+          <t>ETOH_016</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>low_confidence_but_included</t>
+          <t>same_pathway_main_and_reject</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>1 included rows</t>
+          <t>P6</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>{'final_mentioned_pathways': 'P1;P5', 'final_main_pathways': 'P1;P5', 'final_rejected_pathways': 'P5', 'ethanol_specific_level': 'yes', 'main_evidence_basis': 'DFT;DFT;operando/spectroscopy;operando/spectroscopy;operando/spectroscopy;product inference;unknown', 'ai_paper_reason': 'Sentence-level AI review found main-pathway evidence for P1;P5.', 'ai_paper_confidence': 'low', 'final_include': 'yes'}</t>
+          <t>{'final_mentioned_pathways': 'P1;P3;P6', 'final_main_pathways': 'P1;P3;P6', 'final_rejected_pathways': 'P6', 'ethanol_specific_level': 'partial', 'main_evidence_basis': 'mixed', 'ai_paper_reason': '该文献主要基于原位拉曼光谱（SERS）和DFT计算，识别了CO2还原制乙烯和乙醇的关键中间体。统计句显示P1（OCCO路径）、P3（*CHCO→*OCHCH2路径）和P6（*OCHCH路径）是主要提及路径，其中P3和P6明确指向乙醇，P1主要指向乙烯。同时，DFT计算排除了P6（CO-CH耦合）在缺陷位上的主导作用，但实验SERS证实了*OCHCH中间体。因此，文献级路径存在部分冲突，但整体上乙醇路径证据明确。', 'ai_paper_confidence': 'medium', 'final_include': 'yes'}</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>ETOH_009</t>
+          <t>ETOH_023</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -529,430 +529,56 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>P1;P2;P5</t>
+          <t>P1;P3;P4</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>{'final_mentioned_pathways': 'P1;P2;P5', 'final_main_pathways': 'P1;P2;P5', 'final_rejected_pathways': nan, 'ethanol_specific_level': 'yes', 'main_evidence_basis': 'DFT;DFT;operando/spectroscopy;isotope;product inference;unknown', 'ai_paper_reason': 'Sentence-level AI review found main-pathway evidence for P1;P2;P5.', 'ai_paper_confidence': 'low', 'final_include': 'yes'}</t>
+          <t>{'final_mentioned_pathways': 'P1;P3;P4', 'final_main_pathways': 'P1;P3;P4', 'final_rejected_pathways': nan, 'ethanol_specific_level': 'yes', 'main_evidence_basis': 'mixed', 'ai_paper_reason': 'This paper focuses on electrocatalytic CO2 reduction to ethanol via subsurface Co-doped CuS catalyst. The main pathways involve asymmetric C-C coupling (*CO + *COH → *OCCOH) and subsequent hydrogenation steps to ethanol (P1, P3, P4), supported by DFT calculations and in-situ FTIR spectroscopy. Key evidence includes explicit ethanol pathway in S0246 and shared intermediate *CHCHO in S0040.', 'ai_paper_confidence': 'medium', 'final_include': 'yes'}</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>ETOH_009</t>
+          <t>ETOH_024</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>low_confidence_but_included</t>
+          <t>multiple_main_pathways</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>1 included rows</t>
+          <t>P1;P2</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>{'final_mentioned_pathways': 'P1;P2;P5', 'final_main_pathways': 'P1;P2;P5', 'final_rejected_pathways': nan, 'ethanol_specific_level': 'yes', 'main_evidence_basis': 'DFT;DFT;operando/spectroscopy;isotope;product inference;unknown', 'ai_paper_reason': 'Sentence-level AI review found main-pathway evidence for P1;P2;P5.', 'ai_paper_confidence': 'low', 'final_include': 'yes'}</t>
+          <t>{'final_mentioned_pathways': 'P1;P2', 'final_main_pathways': 'P1;P2', 'final_rejected_pathways': nan, 'ethanol_specific_level': 'yes', 'main_evidence_basis': 'mixed', 'ai_paper_reason': '通过DFT和原位光谱证实CA分子促进*OC2H3中间体C-O键保留，有利于乙醇生成，主要路径为P1和P2。', 'ai_paper_confidence': 'high', 'final_include': 'yes'}</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>ETOH_011</t>
+          <t>ETOH_B2_017</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>same_pathway_main_and_reject</t>
+          <t>multiple_main_pathways</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P1;P2;P3</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>{'final_mentioned_pathways': 'P1', 'final_main_pathways': 'P1', 'final_rejected_pathways': 'P1', 'ethanol_specific_level': 'yes', 'main_evidence_basis': 'operando/spectroscopy;operando/spectroscopy;product inference;product inference', 'ai_paper_reason': 'Sentence-level AI review found main-pathway evidence for P1.', 'ai_paper_confidence': 'low', 'final_include': 'yes'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>ETOH_011</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>low_confidence_but_included</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>2 included rows</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>{'final_mentioned_pathways': 'P1', 'final_main_pathways': 'P1', 'final_rejected_pathways': 'P1', 'ethanol_specific_level': 'yes', 'main_evidence_basis': 'operando/spectroscopy;operando/spectroscopy;product inference;product inference', 'ai_paper_reason': 'Sentence-level AI review found main-pathway evidence for P1.', 'ai_paper_confidence': 'low', 'final_include': 'yes'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>ETOH_012</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>low_confidence_but_included</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>2 included rows</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>{'final_mentioned_pathways': 'P1;P5', 'final_main_pathways': 'P5', 'final_rejected_pathways': 'P1', 'ethanol_specific_level': 'yes', 'main_evidence_basis': 'product inference;review', 'ai_paper_reason': 'Sentence-level AI review found main-pathway evidence for P5.', 'ai_paper_confidence': 'low', 'final_include': 'yes'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>ETOH_014</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>low_confidence_but_included</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>1 included rows</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>{'final_mentioned_pathways': 'P1', 'final_main_pathways': nan, 'final_rejected_pathways': nan, 'ethanol_specific_level': 'yes', 'main_evidence_basis': 'product inference', 'ai_paper_reason': 'Sentence-level AI review found pathway mentions for P1, but no main-pathway claim.', 'ai_paper_confidence': 'low', 'final_include': 'yes'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>ETOH_016</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>multiple_main_pathways</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>P1;P3;P5</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>{'final_mentioned_pathways': 'P1;P2;P3;P5;P6', 'final_main_pathways': 'P1;P3;P5', 'final_rejected_pathways': nan, 'ethanol_specific_level': 'yes', 'main_evidence_basis': 'DFT;isotope;DFT;operando/spectroscopy;DFT;operando/spectroscopy;isotope;product inference;DFT;operando/spectroscopy;product inference;DFT;product inference;operando/spectroscopy;operando/spectroscopy;isotope;operando/spectroscopy;product inference;product inference;unknown', 'ai_paper_reason': 'Sentence-level AI review found main-pathway evidence for P1;P3;P5.', 'ai_paper_confidence': 'low', 'final_include': 'yes'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>ETOH_016</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>low_confidence_but_included</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>4 included rows</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>{'final_mentioned_pathways': 'P1;P2;P3;P5;P6', 'final_main_pathways': 'P1;P3;P5', 'final_rejected_pathways': nan, 'ethanol_specific_level': 'yes', 'main_evidence_basis': 'DFT;isotope;DFT;operando/spectroscopy;DFT;operando/spectroscopy;isotope;product inference;DFT;operando/spectroscopy;product inference;DFT;product inference;operando/spectroscopy;operando/spectroscopy;isotope;operando/spectroscopy;product inference;product inference;unknown', 'ai_paper_reason': 'Sentence-level AI review found main-pathway evidence for P1;P3;P5.', 'ai_paper_confidence': 'low', 'final_include': 'yes'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>ETOH_017</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>multiple_main_pathways</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>P1;P2</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>{'final_mentioned_pathways': 'P1;P2;P5', 'final_main_pathways': 'P1;P2', 'final_rejected_pathways': nan, 'ethanol_specific_level': 'yes', 'main_evidence_basis': 'DFT;operando/spectroscopy;DFT;operando/spectroscopy;isotope;DFT;operando/spectroscopy;isotope;product inference;DFT;operando/spectroscopy;product inference;operando/spectroscopy;operando/spectroscopy;product inference;unknown', 'ai_paper_reason': 'Sentence-level AI review found main-pathway evidence for P1;P2.', 'ai_paper_confidence': 'low', 'final_include': 'yes'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>ETOH_017</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>low_confidence_but_included</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>1 included rows</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>{'final_mentioned_pathways': 'P1;P2;P5', 'final_main_pathways': 'P1;P2', 'final_rejected_pathways': nan, 'ethanol_specific_level': 'yes', 'main_evidence_basis': 'DFT;operando/spectroscopy;DFT;operando/spectroscopy;isotope;DFT;operando/spectroscopy;isotope;product inference;DFT;operando/spectroscopy;product inference;operando/spectroscopy;operando/spectroscopy;product inference;unknown', 'ai_paper_reason': 'Sentence-level AI review found main-pathway evidence for P1;P2.', 'ai_paper_confidence': 'low', 'final_include': 'yes'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>ETOH_024</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>multiple_main_pathways</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>P1;P2</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>{'final_mentioned_pathways': 'P1;P2;P5', 'final_main_pathways': 'P1;P2', 'final_rejected_pathways': 'P1;P2;P5', 'ethanol_specific_level': 'yes', 'main_evidence_basis': 'DFT;operando/spectroscopy;product inference;DFT;product inference;operando/spectroscopy;product inference;product inference', 'ai_paper_reason': 'Sentence-level AI review found main-pathway evidence for P1;P2.', 'ai_paper_confidence': 'low', 'final_include': 'yes'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>ETOH_024</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>same_pathway_main_and_reject</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>P1;P2</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>{'final_mentioned_pathways': 'P1;P2;P5', 'final_main_pathways': 'P1;P2', 'final_rejected_pathways': 'P1;P2;P5', 'ethanol_specific_level': 'yes', 'main_evidence_basis': 'DFT;operando/spectroscopy;product inference;DFT;product inference;operando/spectroscopy;product inference;product inference', 'ai_paper_reason': 'Sentence-level AI review found main-pathway evidence for P1;P2.', 'ai_paper_confidence': 'low', 'final_include': 'yes'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>ETOH_024</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>low_confidence_but_included</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>1 included rows</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>{'final_mentioned_pathways': 'P1;P2;P5', 'final_main_pathways': 'P1;P2', 'final_rejected_pathways': 'P1;P2;P5', 'ethanol_specific_level': 'yes', 'main_evidence_basis': 'DFT;operando/spectroscopy;product inference;DFT;product inference;operando/spectroscopy;product inference;product inference', 'ai_paper_reason': 'Sentence-level AI review found main-pathway evidence for P1;P2.', 'ai_paper_confidence': 'low', 'final_include': 'yes'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>ETOH_B2_005</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>low_confidence_but_included</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>1 included rows</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>{'final_mentioned_pathways': 'P5', 'final_main_pathways': 'P5', 'final_rejected_pathways': nan, 'ethanol_specific_level': 'yes', 'main_evidence_basis': 'DFT;operando/spectroscopy;product inference;operando/spectroscopy;product inference', 'ai_paper_reason': 'Sentence-level AI review found main-pathway evidence for P5.', 'ai_paper_confidence': 'low', 'final_include': 'yes'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>ETOH_B2_011</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>multiple_main_pathways</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>P1;P5</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>{'final_mentioned_pathways': 'P1;P4;P5', 'final_main_pathways': 'P1;P5', 'final_rejected_pathways': 'P1', 'ethanol_specific_level': 'yes', 'main_evidence_basis': 'DFT;DFT;operando/spectroscopy;DFT;product inference;operando/spectroscopy;product inference;unknown', 'ai_paper_reason': 'Sentence-level AI review found main-pathway evidence for P1;P5.', 'ai_paper_confidence': 'low', 'final_include': 'yes'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>ETOH_B2_011</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>same_pathway_main_and_reject</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>{'final_mentioned_pathways': 'P1;P4;P5', 'final_main_pathways': 'P1;P5', 'final_rejected_pathways': 'P1', 'ethanol_specific_level': 'yes', 'main_evidence_basis': 'DFT;DFT;operando/spectroscopy;DFT;product inference;operando/spectroscopy;product inference;unknown', 'ai_paper_reason': 'Sentence-level AI review found main-pathway evidence for P1;P5.', 'ai_paper_confidence': 'low', 'final_include': 'yes'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>ETOH_B2_011</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>low_confidence_but_included</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>2 included rows</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>{'final_mentioned_pathways': 'P1;P4;P5', 'final_main_pathways': 'P1;P5', 'final_rejected_pathways': 'P1', 'ethanol_specific_level': 'yes', 'main_evidence_basis': 'DFT;DFT;operando/spectroscopy;DFT;product inference;operando/spectroscopy;product inference;unknown', 'ai_paper_reason': 'Sentence-level AI review found main-pathway evidence for P1;P5.', 'ai_paper_confidence': 'low', 'final_include': 'yes'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>ETOH_B2_012</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>low_confidence_but_included</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>1 included rows</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>{'final_mentioned_pathways': 'P1', 'final_main_pathways': 'P1', 'final_rejected_pathways': nan, 'ethanol_specific_level': 'yes', 'main_evidence_basis': 'isotope;product inference', 'ai_paper_reason': 'Sentence-level AI review found main-pathway evidence for P1.', 'ai_paper_confidence': 'low', 'final_include': 'yes'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>ETOH_B2_015</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>low_confidence_but_included</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>1 included rows</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>{'final_mentioned_pathways': 'P5', 'final_main_pathways': nan, 'final_rejected_pathways': nan, 'ethanol_specific_level': 'yes', 'main_evidence_basis': 'DFT;product inference', 'ai_paper_reason': 'Sentence-level AI review found pathway mentions for P5, but no main-pathway claim.', 'ai_paper_confidence': 'low', 'final_include': 'yes'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>ETOH_B2_017</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>low_confidence_but_included</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>1 included rows</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>{'final_mentioned_pathways': 'P1;P2;P3', 'final_main_pathways': 'P2', 'final_rejected_pathways': nan, 'ethanol_specific_level': 'yes', 'main_evidence_basis': 'DFT;operando/spectroscopy;DFT;operando/spectroscopy;product inference;DFT;product inference;operando/spectroscopy;operando/spectroscopy;product inference;unknown', 'ai_paper_reason': 'Sentence-level AI review found main-pathway evidence for P2.', 'ai_paper_confidence': 'low', 'final_include': 'yes'}</t>
+          <t>{'final_mentioned_pathways': 'P1;P2;P3', 'final_main_pathways': 'P1;P2;P3', 'final_rejected_pathways': nan, 'ethanol_specific_level': 'partial', 'main_evidence_basis': 'mixed', 'ai_paper_reason': 'The paper focuses on low-coordinated Cu catalysts for CO2 reduction to C2+ alcohols, primarily ethanol. DFT calculations and operando Raman spectroscopy identify pathways P1 (*OCCOH intermediate via *CO-COH coupling), P2 (*CH2CO intermediate), and P3 (*CO-COH coupling) as main routes. Evidence includes DFT energy barriers and spectroscopic detection of key intermediates (*OCCOH, *CHO, *OCH2CH3). While ethanol is the dominant product (FE ~56%), the paper often refers to C2+ alcohols generally, leading to a partial ethanol-specific level.', 'ai_paper_confidence': 'medium', 'final_include': 'yes'}</t>
         </is>
       </c>
     </row>

--- a/05_statistics/pathway_conflict_report.xlsx
+++ b/05_statistics/pathway_conflict_report.xlsx
@@ -468,7 +468,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>{'final_mentioned_pathways': 'P2;P5', 'final_main_pathways': 'P2;P5', 'final_rejected_pathways': nan, 'ethanol_specific_level': 'yes', 'main_evidence_basis': 'mixed', 'ai_paper_reason': 'The paper proposes a tandem catalyst with dual active sites (Sn and O) that enable C-C coupling between *CHO and *CO(OH) (P2) and between formate/HCOOH and *CO(OH) (P5) to form ethanol. Evidence includes DFT calculations, isotope labeling, and product distribution experiments.', 'ai_paper_confidence': 'high', 'final_include': 'yes'}</t>
+          <t>{'final_mentioned_pathways': 'P2;P5', 'final_main_pathways': 'P2;P5', 'final_rejected_pathways': nan, 'ethanol_specific_level': 'yes', 'main_evidence_basis': 'mixed', 'ai_paper_reason': '该文献主要报道了Sn基串联催化剂将CO2还原为乙醇，提出了两种主要路径：P2 (*CHO和*CO(OH)偶联)和P5 (甲酸/碳酸氢盐中间体与CO偶联)。通过DFT计算、同位素标记实验和产物分布分析证实了这些路径，所有证据均明确指向乙醇生成。', 'ai_paper_confidence': 'high', 'final_include': 'yes'}</t>
         </is>
       </c>
     </row>
@@ -490,7 +490,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>{'final_mentioned_pathways': 'P1;P3;P6', 'final_main_pathways': 'P1;P3;P6', 'final_rejected_pathways': 'P6', 'ethanol_specific_level': 'partial', 'main_evidence_basis': 'mixed', 'ai_paper_reason': '该文献主要基于原位拉曼光谱（SERS）和DFT计算，识别了CO2还原制乙烯和乙醇的关键中间体。统计句显示P1（OCCO路径）、P3（*CHCO→*OCHCH2路径）和P6（*OCHCH路径）是主要提及路径，其中P3和P6明确指向乙醇，P1主要指向乙烯。同时，DFT计算排除了P6（CO-CH耦合）在缺陷位上的主导作用，但实验SERS证实了*OCHCH中间体。因此，文献级路径存在部分冲突，但整体上乙醇路径证据明确。', 'ai_paper_confidence': 'medium', 'final_include': 'yes'}</t>
+          <t>{'final_mentioned_pathways': 'P1; P3; P6', 'final_main_pathways': 'P1; P3; P6', 'final_rejected_pathways': 'P6', 'ethanol_specific_level': 'partial', 'main_evidence_basis': 'mixed', 'ai_paper_reason': 'Main pathways P1, P3, P6 are supported by operando spectroscopy (Raman/SERS) identifying *OCCO(H), *CHCO reduction to *OCHCH2, and *OCHCH intermediates. However, P6 is also rejected by DFT simulations on distorted sites, creating a conflict. Ethanol is specifically addressed but some P1 evidence relates to ethylene only.', 'ai_paper_confidence': 'medium', 'final_include': 'yes'}</t>
         </is>
       </c>
     </row>
@@ -512,7 +512,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>{'final_mentioned_pathways': 'P1;P3;P6', 'final_main_pathways': 'P1;P3;P6', 'final_rejected_pathways': 'P6', 'ethanol_specific_level': 'partial', 'main_evidence_basis': 'mixed', 'ai_paper_reason': '该文献主要基于原位拉曼光谱（SERS）和DFT计算，识别了CO2还原制乙烯和乙醇的关键中间体。统计句显示P1（OCCO路径）、P3（*CHCO→*OCHCH2路径）和P6（*OCHCH路径）是主要提及路径，其中P3和P6明确指向乙醇，P1主要指向乙烯。同时，DFT计算排除了P6（CO-CH耦合）在缺陷位上的主导作用，但实验SERS证实了*OCHCH中间体。因此，文献级路径存在部分冲突，但整体上乙醇路径证据明确。', 'ai_paper_confidence': 'medium', 'final_include': 'yes'}</t>
+          <t>{'final_mentioned_pathways': 'P1; P3; P6', 'final_main_pathways': 'P1; P3; P6', 'final_rejected_pathways': 'P6', 'ethanol_specific_level': 'partial', 'main_evidence_basis': 'mixed', 'ai_paper_reason': 'Main pathways P1, P3, P6 are supported by operando spectroscopy (Raman/SERS) identifying *OCCO(H), *CHCO reduction to *OCHCH2, and *OCHCH intermediates. However, P6 is also rejected by DFT simulations on distorted sites, creating a conflict. Ethanol is specifically addressed but some P1 evidence relates to ethylene only.', 'ai_paper_confidence': 'medium', 'final_include': 'yes'}</t>
         </is>
       </c>
     </row>
@@ -534,7 +534,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>{'final_mentioned_pathways': 'P1;P3;P4', 'final_main_pathways': 'P1;P3;P4', 'final_rejected_pathways': nan, 'ethanol_specific_level': 'yes', 'main_evidence_basis': 'mixed', 'ai_paper_reason': 'This paper focuses on electrocatalytic CO2 reduction to ethanol via subsurface Co-doped CuS catalyst. The main pathways involve asymmetric C-C coupling (*CO + *COH → *OCCOH) and subsequent hydrogenation steps to ethanol (P1, P3, P4), supported by DFT calculations and in-situ FTIR spectroscopy. Key evidence includes explicit ethanol pathway in S0246 and shared intermediate *CHCHO in S0040.', 'ai_paper_confidence': 'medium', 'final_include': 'yes'}</t>
+          <t>{'final_mentioned_pathways': 'P1;P3;P4', 'final_main_pathways': 'P1;P3;P4', 'final_rejected_pathways': nan, 'ethanol_specific_level': 'yes', 'main_evidence_basis': 'DFT', 'ai_paper_reason': '主要基于DFT计算和in-situ FTIR验证，提出了从CO2到乙醇的完整路径，包括*OCCOH不对称偶联和*CHCHO中间体转化。主路径为P1,P3,P4。', 'ai_paper_confidence': 'high', 'final_include': 'yes'}</t>
         </is>
       </c>
     </row>
@@ -556,7 +556,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>{'final_mentioned_pathways': 'P1;P2', 'final_main_pathways': 'P1;P2', 'final_rejected_pathways': nan, 'ethanol_specific_level': 'yes', 'main_evidence_basis': 'mixed', 'ai_paper_reason': '通过DFT和原位光谱证实CA分子促进*OC2H3中间体C-O键保留，有利于乙醇生成，主要路径为P1和P2。', 'ai_paper_confidence': 'high', 'final_include': 'yes'}</t>
+          <t>{'final_mentioned_pathways': 'P1;P2', 'final_main_pathways': 'P1;P2', 'final_rejected_pathways': nan, 'ethanol_specific_level': 'yes', 'main_evidence_basis': 'mixed', 'ai_paper_reason': '论文通过DFT和原位拉曼光谱确认了*OCCOH和*OC2H5中间体，并在CA存在下促进乙醇生成，因此主要路径为P1和P2。', 'ai_paper_confidence': 'high', 'final_include': 'yes'}</t>
         </is>
       </c>
     </row>
@@ -578,7 +578,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>{'final_mentioned_pathways': 'P1;P2;P3', 'final_main_pathways': 'P1;P2;P3', 'final_rejected_pathways': nan, 'ethanol_specific_level': 'partial', 'main_evidence_basis': 'mixed', 'ai_paper_reason': 'The paper focuses on low-coordinated Cu catalysts for CO2 reduction to C2+ alcohols, primarily ethanol. DFT calculations and operando Raman spectroscopy identify pathways P1 (*OCCOH intermediate via *CO-COH coupling), P2 (*CH2CO intermediate), and P3 (*CO-COH coupling) as main routes. Evidence includes DFT energy barriers and spectroscopic detection of key intermediates (*OCCOH, *CHO, *OCH2CH3). While ethanol is the dominant product (FE ~56%), the paper often refers to C2+ alcohols generally, leading to a partial ethanol-specific level.', 'ai_paper_confidence': 'medium', 'final_include': 'yes'}</t>
+          <t>{'final_mentioned_pathways': 'P1;P2;P3', 'final_main_pathways': 'P1;P2;P3', 'final_rejected_pathways': nan, 'ethanol_specific_level': 'partial', 'main_evidence_basis': 'mixed', 'ai_paper_reason': 'The paper presents DFT calculations and operando Raman spectroscopy to elucidate pathways for CO2 reduction to C2+ alcohols on Cu/Cu2O catalysts. Key evidence supports *CO-COH coupling (P3) and *OCCOH intermediate (P1) for ethanol formation, with minor mention of *CH2CO affinity (P2). Although ethanol is a major product (FE ~56%), some evidence is generalized to C2+ alcohols, leading to partial ethanol specificity.', 'ai_paper_confidence': 'medium', 'final_include': 'yes'}</t>
         </is>
       </c>
     </row>
